--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_Costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_Costs_OMOP.xlsx
@@ -358,7 +358,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>n_exposed</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -413,38 +413,26 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>20512</v>
-      </c>
       <c r="B2">
-        <v>1280.12</v>
+        <v>1258.05</v>
       </c>
       <c r="C2">
-        <v>38.6</v>
+        <v>12.88</v>
       </c>
       <c r="D2">
-        <v>39504.05</v>
+        <v>39835.09</v>
       </c>
       <c r="E2">
-        <v>1607.6</v>
+        <v>1557.78</v>
       </c>
       <c r="F2">
-        <v>831.36</v>
+        <v>832.08</v>
       </c>
       <c r="G2">
-        <v>472.31</v>
+        <v>470.01</v>
       </c>
       <c r="H2">
-        <v>1571.98</v>
-      </c>
-      <c r="I2">
-        <v>11.22</v>
-      </c>
-      <c r="J2">
-        <v>1258.12</v>
-      </c>
-      <c r="K2">
-        <v>1302.13</v>
+        <v>1543.5</v>
       </c>
     </row>
   </sheetData>
@@ -460,7 +448,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>n_exposed</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -515,38 +503,26 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>22900</v>
-      </c>
       <c r="B2">
-        <v>1146.43</v>
+        <v>1126.65</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>39504.05</v>
+        <v>39835.09</v>
       </c>
       <c r="E2">
-        <v>1570.9</v>
+        <v>1523.57</v>
       </c>
       <c r="F2">
-        <v>713.58</v>
+        <v>707.36</v>
       </c>
       <c r="G2">
-        <v>332.54</v>
+        <v>332.83</v>
       </c>
       <c r="H2">
-        <v>1443.38</v>
-      </c>
-      <c r="I2">
-        <v>10.38</v>
-      </c>
-      <c r="J2">
-        <v>1126.09</v>
-      </c>
-      <c r="K2">
-        <v>1166.78</v>
+        <v>1420.77</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_Costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_Costs_OMOP.xlsx
@@ -414,25 +414,25 @@
     </row>
     <row r="2">
       <c r="B2">
-        <v>1258.05</v>
+        <v>1254.97</v>
       </c>
       <c r="C2">
         <v>12.88</v>
       </c>
       <c r="D2">
-        <v>39835.09</v>
+        <v>39771.67</v>
       </c>
       <c r="E2">
-        <v>1557.78</v>
+        <v>1558.96</v>
       </c>
       <c r="F2">
-        <v>832.08</v>
+        <v>831.36</v>
       </c>
       <c r="G2">
-        <v>470.01</v>
+        <v>468.74</v>
       </c>
       <c r="H2">
-        <v>1543.5</v>
+        <v>1538.77</v>
       </c>
     </row>
   </sheetData>
@@ -504,25 +504,25 @@
     </row>
     <row r="2">
       <c r="B2">
-        <v>1126.65</v>
+        <v>1123.9</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>39835.09</v>
+        <v>39771.67</v>
       </c>
       <c r="E2">
-        <v>1523.57</v>
+        <v>1524.41</v>
       </c>
       <c r="F2">
-        <v>707.36</v>
+        <v>703.6900000000001</v>
       </c>
       <c r="G2">
-        <v>332.83</v>
+        <v>332.54</v>
       </c>
       <c r="H2">
-        <v>1420.77</v>
+        <v>1417.02</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_Costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_Costs_OMOP.xlsx
@@ -413,8 +413,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2">
+        <v>25772345.03</v>
+      </c>
       <c r="B2">
-        <v>1254.97</v>
+        <v>1256.45</v>
       </c>
       <c r="C2">
         <v>12.88</v>
@@ -423,7 +426,7 @@
         <v>39771.67</v>
       </c>
       <c r="E2">
-        <v>1558.96</v>
+        <v>1560.59</v>
       </c>
       <c r="F2">
         <v>831.36</v>
@@ -432,7 +435,16 @@
         <v>468.74</v>
       </c>
       <c r="H2">
-        <v>1538.77</v>
+        <v>1540.32</v>
+      </c>
+      <c r="I2">
+        <v>0.31</v>
+      </c>
+      <c r="J2">
+        <v>1255.85</v>
+      </c>
+      <c r="K2">
+        <v>1257.05</v>
       </c>
     </row>
   </sheetData>
@@ -503,8 +515,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2">
+        <v>25772345.03</v>
+      </c>
       <c r="B2">
-        <v>1123.9</v>
+        <v>1125.43</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -513,7 +528,7 @@
         <v>39771.67</v>
       </c>
       <c r="E2">
-        <v>1524.41</v>
+        <v>1526.08</v>
       </c>
       <c r="F2">
         <v>703.6900000000001</v>
@@ -522,7 +537,16 @@
         <v>332.54</v>
       </c>
       <c r="H2">
-        <v>1417.02</v>
+        <v>1418.48</v>
+      </c>
+      <c r="I2">
+        <v>0.3</v>
+      </c>
+      <c r="J2">
+        <v>1124.84</v>
+      </c>
+      <c r="K2">
+        <v>1126.02</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_Costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_Costs_OMOP.xlsx
@@ -414,37 +414,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>25772345.03</v>
+        <v>26544143.62</v>
       </c>
       <c r="B2">
-        <v>1256.45</v>
+        <v>1294.08</v>
       </c>
       <c r="C2">
         <v>12.88</v>
       </c>
       <c r="D2">
-        <v>39771.67</v>
+        <v>40482.85</v>
       </c>
       <c r="E2">
-        <v>1560.59</v>
+        <v>1616.75</v>
       </c>
       <c r="F2">
-        <v>831.36</v>
+        <v>834.99</v>
       </c>
       <c r="G2">
-        <v>468.74</v>
+        <v>482.71</v>
       </c>
       <c r="H2">
-        <v>1540.32</v>
+        <v>1592.02</v>
       </c>
       <c r="I2">
         <v>0.31</v>
       </c>
       <c r="J2">
-        <v>1255.85</v>
+        <v>1293.46</v>
       </c>
       <c r="K2">
-        <v>1257.05</v>
+        <v>1294.69</v>
       </c>
     </row>
   </sheetData>
@@ -516,37 +516,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>25772345.03</v>
+        <v>26544143.62</v>
       </c>
       <c r="B2">
-        <v>1125.43</v>
+        <v>1159.13</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>39771.67</v>
+        <v>40482.85</v>
       </c>
       <c r="E2">
-        <v>1526.08</v>
+        <v>1580.42</v>
       </c>
       <c r="F2">
-        <v>703.6900000000001</v>
+        <v>722.37</v>
       </c>
       <c r="G2">
-        <v>332.54</v>
+        <v>333.03</v>
       </c>
       <c r="H2">
-        <v>1418.48</v>
+        <v>1464.73</v>
       </c>
       <c r="I2">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="J2">
-        <v>1124.84</v>
+        <v>1158.53</v>
       </c>
       <c r="K2">
-        <v>1126.02</v>
+        <v>1159.73</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_Costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_Costs_OMOP.xlsx
@@ -358,7 +358,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>n_exposed</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -414,7 +414,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>26544143.62</v>
+        <v>20512</v>
       </c>
       <c r="B2">
         <v>1294.08</v>
@@ -438,13 +438,13 @@
         <v>1592.02</v>
       </c>
       <c r="I2">
-        <v>0.31</v>
+        <v>11.29</v>
       </c>
       <c r="J2">
-        <v>1293.46</v>
+        <v>1271.95</v>
       </c>
       <c r="K2">
-        <v>1294.69</v>
+        <v>1316.21</v>
       </c>
     </row>
   </sheetData>
@@ -460,7 +460,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>n_exposed</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -516,7 +516,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>26544143.62</v>
+        <v>22900</v>
       </c>
       <c r="B2">
         <v>1159.13</v>
@@ -540,13 +540,13 @@
         <v>1464.73</v>
       </c>
       <c r="I2">
-        <v>0.31</v>
+        <v>10.44</v>
       </c>
       <c r="J2">
-        <v>1158.53</v>
+        <v>1138.66</v>
       </c>
       <c r="K2">
-        <v>1159.73</v>
+        <v>1179.6</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_Costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_Costs_OMOP.xlsx
@@ -417,34 +417,34 @@
         <v>20512</v>
       </c>
       <c r="B2">
-        <v>1294.08</v>
+        <v>1314.11</v>
       </c>
       <c r="C2">
         <v>12.88</v>
       </c>
       <c r="D2">
-        <v>40482.85</v>
+        <v>56949.01</v>
       </c>
       <c r="E2">
-        <v>1616.75</v>
+        <v>1726.87</v>
       </c>
       <c r="F2">
-        <v>834.99</v>
+        <v>842.14</v>
       </c>
       <c r="G2">
         <v>482.71</v>
       </c>
       <c r="H2">
-        <v>1592.02</v>
+        <v>1602.23</v>
       </c>
       <c r="I2">
-        <v>11.29</v>
+        <v>12.06</v>
       </c>
       <c r="J2">
-        <v>1271.95</v>
+        <v>1290.48</v>
       </c>
       <c r="K2">
-        <v>1316.21</v>
+        <v>1337.74</v>
       </c>
     </row>
   </sheetData>
@@ -519,34 +519,34 @@
         <v>22900</v>
       </c>
       <c r="B2">
-        <v>1159.13</v>
+        <v>1177.08</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>40482.85</v>
+        <v>56949.01</v>
       </c>
       <c r="E2">
-        <v>1580.42</v>
+        <v>1682.97</v>
       </c>
       <c r="F2">
-        <v>722.37</v>
+        <v>727.1</v>
       </c>
       <c r="G2">
         <v>333.03</v>
       </c>
       <c r="H2">
-        <v>1464.73</v>
+        <v>1478.19</v>
       </c>
       <c r="I2">
-        <v>10.44</v>
+        <v>11.12</v>
       </c>
       <c r="J2">
-        <v>1138.66</v>
+        <v>1155.28</v>
       </c>
       <c r="K2">
-        <v>1179.6</v>
+        <v>1198.87</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_Costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_Costs_OMOP.xlsx
@@ -417,34 +417,34 @@
         <v>20512</v>
       </c>
       <c r="B2">
-        <v>1314.11</v>
+        <v>1284.85</v>
       </c>
       <c r="C2">
-        <v>12.88</v>
+        <v>79.45</v>
       </c>
       <c r="D2">
-        <v>56949.01</v>
+        <v>39077.31</v>
       </c>
       <c r="E2">
-        <v>1726.87</v>
+        <v>1573.95</v>
       </c>
       <c r="F2">
-        <v>842.14</v>
+        <v>815.88</v>
       </c>
       <c r="G2">
-        <v>482.71</v>
+        <v>449.06</v>
       </c>
       <c r="H2">
-        <v>1602.23</v>
+        <v>1618.43</v>
       </c>
       <c r="I2">
-        <v>12.06</v>
+        <v>10.99</v>
       </c>
       <c r="J2">
-        <v>1290.48</v>
+        <v>1263.31</v>
       </c>
       <c r="K2">
-        <v>1337.74</v>
+        <v>1306.39</v>
       </c>
     </row>
   </sheetData>
@@ -519,34 +519,34 @@
         <v>22900</v>
       </c>
       <c r="B2">
-        <v>1177.08</v>
+        <v>1150.87</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>56949.01</v>
+        <v>39077.31</v>
       </c>
       <c r="E2">
-        <v>1682.97</v>
+        <v>1540.51</v>
       </c>
       <c r="F2">
-        <v>727.1</v>
+        <v>748.4299999999999</v>
       </c>
       <c r="G2">
-        <v>333.03</v>
+        <v>299.37</v>
       </c>
       <c r="H2">
-        <v>1478.19</v>
+        <v>1496.87</v>
       </c>
       <c r="I2">
-        <v>11.12</v>
+        <v>10.18</v>
       </c>
       <c r="J2">
-        <v>1155.28</v>
+        <v>1130.92</v>
       </c>
       <c r="K2">
-        <v>1198.87</v>
+        <v>1170.82</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_Costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_Costs_OMOP.xlsx
@@ -417,34 +417,34 @@
         <v>20512</v>
       </c>
       <c r="B2">
-        <v>1284.85</v>
+        <v>1321.8</v>
       </c>
       <c r="C2">
-        <v>79.45</v>
+        <v>12.88</v>
       </c>
       <c r="D2">
-        <v>39077.31</v>
+        <v>44722.05</v>
       </c>
       <c r="E2">
-        <v>1573.95</v>
+        <v>1697.79</v>
       </c>
       <c r="F2">
-        <v>815.88</v>
+        <v>851.61</v>
       </c>
       <c r="G2">
-        <v>449.06</v>
+        <v>482.71</v>
       </c>
       <c r="H2">
-        <v>1618.43</v>
+        <v>1620.15</v>
       </c>
       <c r="I2">
-        <v>10.99</v>
+        <v>11.85</v>
       </c>
       <c r="J2">
-        <v>1263.31</v>
+        <v>1298.57</v>
       </c>
       <c r="K2">
-        <v>1306.39</v>
+        <v>1345.04</v>
       </c>
     </row>
   </sheetData>
@@ -519,34 +519,34 @@
         <v>22900</v>
       </c>
       <c r="B2">
-        <v>1150.87</v>
+        <v>1183.97</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>39077.31</v>
+        <v>44722.05</v>
       </c>
       <c r="E2">
-        <v>1540.51</v>
+        <v>1656.83</v>
       </c>
       <c r="F2">
-        <v>748.4299999999999</v>
+        <v>738.5599999999999</v>
       </c>
       <c r="G2">
-        <v>299.37</v>
+        <v>333.03</v>
       </c>
       <c r="H2">
-        <v>1496.87</v>
+        <v>1488.76</v>
       </c>
       <c r="I2">
-        <v>10.18</v>
+        <v>10.95</v>
       </c>
       <c r="J2">
-        <v>1130.92</v>
+        <v>1162.51</v>
       </c>
       <c r="K2">
-        <v>1170.82</v>
+        <v>1205.43</v>
       </c>
     </row>
   </sheetData>
